--- a/docs/page-copy/02-组织介绍.xlsx
+++ b/docs/page-copy/02-组织介绍.xlsx
@@ -1012,10 +1012,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D27" t="str">
-        <v>Through this partnership, human members acquire Class-C PRCASG abilities: the power to govern attached spirits and to actively improve human health.</v>
+        <v>Through this partnership, human members acquire Class-C PRCASG abilities: the power to govern attached spirits(ghosts) and to actively improve human health.</v>
       </c>
       <c r="E27" t="str">
-        <v>通过该伙伴关系，人类会员获得 C 级PRCASG能力：治理附体灵并主动改善人类健康。</v>
+        <v>通过该伙伴关系，人类会员获得 C 级PRCASG能力：治理附体鬼魂并主动改善人类健康。</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1058,10 +1058,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D29" t="str">
-        <v>Empowered members serve as ambassadors — spreading the truth of the Spirit Realm and spirit life to the world, and leading humanity toward the New ERA.</v>
+        <v>Empowered members serve as ambassadors — spreading the truth of the Spirit Realm and spirit to the world, and leading humanity toward the New ERA.</v>
       </c>
       <c r="E29" t="str">
-        <v>被赋能的会员作为大使——向世界传播灵魂世界与灵体的真相，并引领人类迈向新世纪。</v>
+        <v>被赋能的会员作为大使——向世界传播灵魂世界与灵魂的真相，并引领人类迈向新世纪。</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1426,7 +1426,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D45" t="str">
-        <v>The spiritual realm has various types of master spirits. Among them, some are specifically responsible for helping ASRA members acquire the PRCASG superpower to control ghosts; they are called controllers among the master spirits</v>
+        <v>The spiritual realm has various types of master spirits. Among them, some are specifically responsible for helping ASRA members acquire the PRCASG superpower to control **spirits (ghosts)**; they are called controllers among the master spirits</v>
       </c>
       <c r="E45" t="str">
         <v>灵魂世界有各种类型的高级掌控灵( Master spirit)。其中一部分专门负责帮助ASRA会员获得控制鬼魂的PRCASG超能力,他们被称为高级掌控灵中的控制者</v>
@@ -1610,7 +1610,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D53" t="str">
-        <v>Members gain the C-level PRCASG special ability to manage attached spirit ghost and improve human health. And independently operate in the physical world and get corresponding compensation.</v>
+        <v>Members gain the C-level PRCASG special ability to manage attached **spirit (ghost)** and improve human health. And independently operate in the physical world and get corresponding compensation.</v>
       </c>
       <c r="E53" t="str">
         <v>成员获得管理附体鬼魂,改善人类健康的C级别PRCASG特别能力。并独立在现实世界运营并获得相应的报酬</v>

--- a/docs/page-copy/02-组织介绍.xlsx
+++ b/docs/page-copy/02-组织介绍.xlsx
@@ -1012,7 +1012,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D27" t="str">
-        <v>Through this partnership, human members acquire Class-C PRCASG abilities: the power to govern attached spirits(ghosts) and to actively improve human health.</v>
+        <v>Through this partnership, human members acquire C level PRCASG abilities: the power to govern attached spirits(ghosts) and to actively improve human health.</v>
       </c>
       <c r="E27" t="str">
         <v>通过该伙伴关系，人类会员获得 C 级PRCASG能力：治理附体鬼魂并主动改善人类健康。</v>
@@ -1518,7 +1518,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D49" t="str">
-        <v>Woos father and son are the founders of ASRA and the president of the association,they are responsible for the coordination between the two associations, and screen suitable human beings as ambassadors of ASRA in the real world and recommend them to SMSC. After screening by SMSC → empowerment → internship assessment, it officially became a member of ASRA.</v>
+        <v>Woos father and son are the founders of ASRA and the president of the association,they are responsible for the coordination between the two associations, and screen suitable human beings as ambassadors of ASRA in the real world and recommend them to SMSC. After screening by SMSC → empowerment → internship assessment, then officially became a member of ASRA.</v>
       </c>
       <c r="E49" t="str">
         <v>吴氏父子是ASRA的创建者和协会会长。吴氏父子负责两个协会的协调联系，并且在现实世界筛选合适的人类作为 ASRA的使者候选人，并且推荐给SMSC。由 SMSC筛选→赋能→实习考核后正式成为ASRA成员</v>
@@ -1530,7 +1530,7 @@
         <v>siteContent.aboutContent — add 中文/Latin in sheet</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
         <v>aboutContent.founders.storyTeaser</v>
       </c>
@@ -1540,8 +1540,9 @@
       <c r="C50" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D50" t="str">
-        <v>The First Door-opener in the spiritual realm-Legend Collection</v>
+      <c r="D50" t="str" xml:space="preserve">
+        <v xml:space="preserve">The First Door-opener to the spiritual realm
+------Legend Collection</v>
       </c>
       <c r="E50" t="str">
         <v>灵魂世界的首位开门人-----传奇故事总汇</v>
@@ -1702,8 +1703,8 @@
         <v>paragraph / other</v>
       </c>
       <c r="D57" t="str" xml:space="preserve">
-        <v xml:space="preserve">The emergence of AI will inevitably lead to universal unemployment across all of humanity; the deployment of military AI will inevitably lead to humanity's extinction. Humanity stands at the edge of the destruction of the old Era.
-Based on the three documentary series — the Woos Spirit Archive, Woos Spirit Medicine, and the Universal Matrix of Meta Awareness — members are obligated to spread to the 8 billion people of humanity the truth of Spirit and Its Governor, which has been concealed for thousands of years, and to lead humanity toward the Umma New Era.</v>
+        <v xml:space="preserve">The emergence of AI will inevitably lead to mass unemployment among all humans, while its use in military applications will surely result in the extinction of humanity. Mankind stands on the brink of destruction, a process that every planet in the universe must go through as part of its intellectual development. 
+Spirit matter can penetrate not only human flesh brains but also supercomputers that control AI systems. UMMA will not allow AI to destroy humanity. It is the duty of all ASRA members to guide humanity toward understanding true spirit life, the spiritual world, and the Creator UMMA. Only then can humanity be freed from the challenges posed by AI and enter a new era where physical life, spiritual life, and AI coexist in harmony under UMMA.</v>
       </c>
       <c r="E57" t="str" xml:space="preserve">
         <v xml:space="preserve">AI的出现必然导致全人类失业，军事AI的使用必然导致人类的灭亡。人类正处于旧世纪灭亡的边缘，这也是宇宙间每个星球都会经历的智慧发展历程。
